--- a/Analysed/Gemini_gemini-3-pro-preview_cot.xlsx
+++ b/Analysed/Gemini_gemini-3-pro-preview_cot.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J54"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -602,16 +602,16 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H4" t="n">
-        <v>1.547981651376146</v>
+        <v>1.534</v>
       </c>
       <c r="I4" t="n">
-        <v>1.845019330596628</v>
+        <v>1.836613979335589</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1574074074074074</v>
+        <v>0.1651376146788991</v>
       </c>
     </row>
     <row r="5">
@@ -646,16 +646,16 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H5" t="n">
-        <v>1.523529411764706</v>
+        <v>1.501449275362319</v>
       </c>
       <c r="I5" t="n">
-        <v>1.892579161449513</v>
+        <v>1.87881476669102</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3134328358208955</v>
+        <v>0.3235294117647059</v>
       </c>
     </row>
     <row r="6">
@@ -693,10 +693,10 @@
         <v>51</v>
       </c>
       <c r="H6" t="n">
-        <v>2.539607843137255</v>
+        <v>2.541764705882353</v>
       </c>
       <c r="I6" t="n">
-        <v>2.796649956714668</v>
+        <v>2.79973703246937</v>
       </c>
       <c r="J6" t="n">
         <v>0.38</v>
@@ -1042,16 +1042,16 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H14" t="n">
-        <v>1.495329153605016</v>
+        <v>1.5</v>
       </c>
       <c r="I14" t="n">
-        <v>1.751424409106784</v>
+        <v>1.756655736050749</v>
       </c>
       <c r="J14" t="n">
-        <v>0.06289308176100629</v>
+        <v>0.06583072100313479</v>
       </c>
     </row>
     <row r="15">
@@ -1262,16 +1262,16 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H19" t="n">
-        <v>1.741621621621622</v>
+        <v>1.776578947368421</v>
       </c>
       <c r="I19" t="n">
-        <v>2.166514201149806</v>
+        <v>2.195059644316132</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5277777777777778</v>
+        <v>0.5405405405405406</v>
       </c>
     </row>
     <row r="20">
@@ -1438,16 +1438,16 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H23" t="n">
-        <v>18.22513513513514</v>
+        <v>18.15868421052632</v>
       </c>
       <c r="I23" t="n">
-        <v>18.35761120596003</v>
+        <v>18.29262139138131</v>
       </c>
       <c r="J23" t="n">
-        <v>0.5277777777777778</v>
+        <v>0.5405405405405406</v>
       </c>
     </row>
     <row r="24">
@@ -1570,16 +1570,16 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="H26" t="n">
-        <v>25.07754098360655</v>
+        <v>25.05047999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>25.09107695223445</v>
+        <v>25.06429953539496</v>
       </c>
       <c r="J26" t="n">
-        <v>0.2231404958677686</v>
+        <v>0.2419354838709677</v>
       </c>
     </row>
     <row r="27">
@@ -1834,16 +1834,16 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="H32" t="n">
-        <v>16.04169491525423</v>
+        <v>16.10512396694215</v>
       </c>
       <c r="I32" t="n">
-        <v>16.12774359789125</v>
+        <v>16.19360280792469</v>
       </c>
       <c r="J32" t="n">
-        <v>0.188034188034188</v>
+        <v>0.2083333333333333</v>
       </c>
     </row>
     <row r="33">
@@ -1878,16 +1878,16 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H33" t="n">
-        <v>15.48030303030303</v>
+        <v>15.69027777777777</v>
       </c>
       <c r="I33" t="n">
-        <v>15.58109479951634</v>
+        <v>15.796823696202</v>
       </c>
       <c r="J33" t="n">
-        <v>0.2307692307692308</v>
+        <v>0.2957746478873239</v>
       </c>
     </row>
     <row r="34">
@@ -2054,16 +2054,16 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="H37" t="n">
-        <v>17.51052631578947</v>
+        <v>19.01612903225806</v>
       </c>
       <c r="I37" t="n">
-        <v>17.63837025530301</v>
+        <v>19.18219100136642</v>
       </c>
       <c r="J37" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="38">
@@ -2142,13 +2142,13 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H39" t="n">
-        <v>28.4705</v>
+        <v>28.62835820895522</v>
       </c>
       <c r="I39" t="n">
-        <v>32.95750039065463</v>
+        <v>33.14849796616636</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2186,16 +2186,16 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H40" t="n">
-        <v>9.450000000000001</v>
+        <v>9.645454545454548</v>
       </c>
       <c r="I40" t="n">
-        <v>11.1871993648826</v>
+        <v>11.41476332729601</v>
       </c>
       <c r="J40" t="n">
-        <v>0.1495327102803738</v>
+        <v>0.1651376146788991</v>
       </c>
     </row>
     <row r="41">
@@ -2230,13 +2230,13 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H41" t="n">
-        <v>15.78692307692308</v>
+        <v>16.28975</v>
       </c>
       <c r="I41" t="n">
-        <v>19.32706817141607</v>
+        <v>19.91024045560475</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2274,16 +2274,16 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H42" t="n">
-        <v>9.690697674418606</v>
+        <v>10.16222222222222</v>
       </c>
       <c r="I42" t="n">
-        <v>11.22441483428392</v>
+        <v>11.77723038560236</v>
       </c>
       <c r="J42" t="n">
-        <v>0.2380952380952381</v>
+        <v>0.2727272727272727</v>
       </c>
     </row>
     <row r="43">
@@ -2318,16 +2318,16 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="H43" t="n">
-        <v>37.43392857142857</v>
+        <v>33.29305555555555</v>
       </c>
       <c r="I43" t="n">
-        <v>39.29518686447853</v>
+        <v>35.77035081212124</v>
       </c>
       <c r="J43" t="n">
-        <v>0.3703703703703703</v>
+        <v>0.5142857142857142</v>
       </c>
     </row>
     <row r="44">
@@ -2362,16 +2362,16 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H44" t="n">
-        <v>23.17314814814815</v>
+        <v>23.15107692307692</v>
       </c>
       <c r="I44" t="n">
-        <v>23.63170077420331</v>
+        <v>23.61200211105165</v>
       </c>
       <c r="J44" t="n">
-        <v>0.07739938080495357</v>
+        <v>0.08024691358024691</v>
       </c>
     </row>
     <row r="45">
@@ -2402,20 +2402,20 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>OPENING-CLOSING_OPENING-CLOSING_V3_1.7 divisions_per_second</t>
+          <t>OPENING-CLOSING_OPENING-CLOSING_V2_0.8 divisions_per_second</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>110</v>
+        <v>205</v>
       </c>
       <c r="H45" t="n">
-        <v>22.19818181818182</v>
+        <v>20.84512195121951</v>
       </c>
       <c r="I45" t="n">
-        <v>22.75657463439762</v>
+        <v>21.38716580044233</v>
       </c>
       <c r="J45" t="n">
-        <v>0.1743119266055046</v>
+        <v>0.1274509803921569</v>
       </c>
     </row>
     <row r="46">
@@ -2446,20 +2446,20 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>OPENING-CLOSING_OPENING-CLOSING_V4_2.5 divisions_per_second</t>
+          <t>OPENING-CLOSING_OPENING-CLOSING_V3_1.7 divisions_per_second</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="H46" t="n">
-        <v>18.73764705882353</v>
+        <v>22.19818181818182</v>
       </c>
       <c r="I46" t="n">
-        <v>19.49407578184294</v>
+        <v>22.75657463439762</v>
       </c>
       <c r="J46" t="n">
-        <v>0.3690476190476191</v>
+        <v>0.1743119266055046</v>
       </c>
     </row>
     <row r="47">
@@ -2490,20 +2490,20 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>OPENING-CLOSING_OPENING-CLOSING_V5_5 divisions_per_second</t>
+          <t>OPENING-CLOSING_OPENING-CLOSING_V4_2.5 divisions_per_second</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="H47" t="n">
-        <v>21.46272727272726</v>
+        <v>18.73764705882353</v>
       </c>
       <c r="I47" t="n">
-        <v>22.20400262851886</v>
+        <v>19.49407578184294</v>
       </c>
       <c r="J47" t="n">
-        <v>0.4074074074074074</v>
+        <v>0.3690476190476191</v>
       </c>
     </row>
     <row r="48">
@@ -2534,20 +2534,20 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>OPENING-CLOSING_OPENING-CLOSING_V6_10 divisions_per_second</t>
+          <t>OPENING-CLOSING_OPENING-CLOSING_V5_5 divisions_per_second</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="H48" t="n">
-        <v>14.7329268292683</v>
+        <v>21.46272727272726</v>
       </c>
       <c r="I48" t="n">
-        <v>16.02529882526452</v>
+        <v>22.20400262851886</v>
       </c>
       <c r="J48" t="n">
-        <v>0.55</v>
+        <v>0.4074074074074074</v>
       </c>
     </row>
     <row r="49">
@@ -2573,25 +2573,25 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>OPENING</t>
+          <t>OPENING-CLOSING</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>OPENING_OPENING_V1_0.5 divisions_per_second</t>
+          <t>OPENING-CLOSING_OPENING-CLOSING_V6_10 divisions_per_second</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>315</v>
+        <v>41</v>
       </c>
       <c r="H49" t="n">
-        <v>26.49380952380952</v>
+        <v>14.7329268292683</v>
       </c>
       <c r="I49" t="n">
-        <v>28.0033418924038</v>
+        <v>16.02529882526452</v>
       </c>
       <c r="J49" t="n">
-        <v>0.04458598726114649</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="50">
@@ -2622,20 +2622,20 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>OPENING_OPENING_V2_0.8 divisions_per_second</t>
+          <t>OPENING_OPENING_V1_0.5 divisions_per_second</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>193</v>
+        <v>315</v>
       </c>
       <c r="H50" t="n">
-        <v>16.18886010362694</v>
+        <v>26.49380952380952</v>
       </c>
       <c r="I50" t="n">
-        <v>16.29668705008138</v>
+        <v>28.0033418924038</v>
       </c>
       <c r="J50" t="n">
-        <v>0.9635416666666666</v>
+        <v>0.04458598726114649</v>
       </c>
     </row>
     <row r="51">
@@ -2666,20 +2666,20 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>OPENING_OPENING_V3_1.7 divisions_per_second</t>
+          <t>OPENING_OPENING_V2_0.8 divisions_per_second</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>106</v>
+        <v>196</v>
       </c>
       <c r="H51" t="n">
-        <v>29.46603773584905</v>
+        <v>16.12627551020408</v>
       </c>
       <c r="I51" t="n">
-        <v>31.07162632151962</v>
+        <v>16.24063901489855</v>
       </c>
       <c r="J51" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.9487179487179487</v>
       </c>
     </row>
     <row r="52">
@@ -2710,20 +2710,20 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>OPENING_OPENING_V4_2.5 divisions_per_second</t>
+          <t>OPENING_OPENING_V3_1.7 divisions_per_second</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="H52" t="n">
-        <v>25.87763157894737</v>
+        <v>29.46603773584905</v>
       </c>
       <c r="I52" t="n">
-        <v>27.87458071433542</v>
+        <v>31.07162632151962</v>
       </c>
       <c r="J52" t="n">
-        <v>0.1866666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
     </row>
     <row r="53">
@@ -2754,20 +2754,20 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>OPENING_OPENING_V5_5 divisions_per_second</t>
+          <t>OPENING_OPENING_V4_2.5 divisions_per_second</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="H53" t="n">
-        <v>30.32553191489363</v>
+        <v>25.87763157894737</v>
       </c>
       <c r="I53" t="n">
-        <v>32.40723684611201</v>
+        <v>27.87458071433542</v>
       </c>
       <c r="J53" t="n">
-        <v>0.3260869565217391</v>
+        <v>0.1866666666666667</v>
       </c>
     </row>
     <row r="54">
@@ -2798,19 +2798,63 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
+          <t>OPENING_OPENING_V5_5 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>48</v>
+      </c>
+      <c r="H54" t="n">
+        <v>30.63541666666667</v>
+      </c>
+      <c r="I54" t="n">
+        <v>32.72480041955947</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0.3404255319148936</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>gemini-3-pro-preview</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>cot</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>3.- Analog Depth Gauge_without vernier</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>OPENING</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
           <t>OPENING_OPENING_V6_10 divisions_per_second</t>
         </is>
       </c>
-      <c r="G54" t="n">
+      <c r="G55" t="n">
         <v>31</v>
       </c>
-      <c r="H54" t="n">
+      <c r="H55" t="n">
         <v>28.95806451612903</v>
       </c>
-      <c r="I54" t="n">
+      <c r="I55" t="n">
         <v>31.55435668503561</v>
       </c>
-      <c r="J54" t="n">
+      <c r="J55" t="n">
         <v>0.4333333333333333</v>
       </c>
     </row>
@@ -2857,14 +2901,14 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13.0934</v>
+        <v>13.2204</v>
       </c>
       <c r="C2" t="n">
-        <v>10.132</v>
+        <v>9.9451</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>13.0934 ± 10.1320</t>
+          <t>13.2204 ± 9.9451</t>
         </is>
       </c>
     </row>
@@ -2875,14 +2919,14 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13.8072</v>
+        <v>13.9479</v>
       </c>
       <c r="C3" t="n">
-        <v>10.6111</v>
+        <v>10.4427</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>13.8072 ± 10.6111</t>
+          <t>13.9479 ± 10.4427</t>
         </is>
       </c>
     </row>
@@ -2893,14 +2937,14 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3324</v>
+        <v>0.3375</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2404</v>
+        <v>0.2435</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.3324 ± 0.2404</t>
+          <t>0.3375 ± 0.2435</t>
         </is>
       </c>
     </row>
@@ -2975,19 +3019,19 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3681</v>
+        <v>3.3624</v>
       </c>
       <c r="E2" t="n">
-        <v>2.3699</v>
+        <v>2.3759</v>
       </c>
       <c r="F2" t="n">
-        <v>3.5838</v>
+        <v>3.5806</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3984</v>
+        <v>0.4014</v>
       </c>
       <c r="H2" t="n">
-        <v>126.2</v>
+        <v>126.5</v>
       </c>
     </row>
     <row r="3">
@@ -3005,19 +3049,19 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4791</v>
+        <v>1.4857</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2128</v>
+        <v>0.2226</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7942</v>
+        <v>1.7999</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2848</v>
+        <v>0.2874</v>
       </c>
       <c r="H3" t="n">
-        <v>124.3</v>
+        <v>124.7</v>
       </c>
     </row>
     <row r="4">
@@ -3065,19 +3109,19 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>12.5837</v>
+        <v>12.5727</v>
       </c>
       <c r="E5" t="n">
-        <v>6.4853</v>
+        <v>6.4726</v>
       </c>
       <c r="F5" t="n">
-        <v>13.23</v>
+        <v>13.2192</v>
       </c>
       <c r="G5" t="n">
-        <v>0.193</v>
+        <v>0.1951</v>
       </c>
       <c r="H5" t="n">
-        <v>54.2</v>
+        <v>54.3</v>
       </c>
     </row>
     <row r="6">
@@ -3095,19 +3139,19 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>16.6752</v>
+        <v>16.9717</v>
       </c>
       <c r="E6" t="n">
-        <v>1.5222</v>
+        <v>1.771</v>
       </c>
       <c r="F6" t="n">
-        <v>16.7947</v>
+        <v>17.099</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4421</v>
+        <v>0.4785</v>
       </c>
       <c r="H6" t="n">
-        <v>53.7</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="7">
@@ -3125,19 +3169,19 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>16.3331</v>
+        <v>16.3286</v>
       </c>
       <c r="E7" t="n">
-        <v>4.728</v>
+        <v>4.7169</v>
       </c>
       <c r="F7" t="n">
-        <v>16.3633</v>
+        <v>16.3588</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5242</v>
+        <v>0.5274</v>
       </c>
       <c r="H7" t="n">
-        <v>62.8</v>
+        <v>63.3</v>
       </c>
     </row>
     <row r="8">
@@ -3155,19 +3199,19 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>21.6055</v>
+        <v>21.1366</v>
       </c>
       <c r="E8" t="n">
-        <v>12.1754</v>
+        <v>10.8921</v>
       </c>
       <c r="F8" t="n">
-        <v>24.0309</v>
+        <v>23.7025</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1348</v>
+        <v>0.1672</v>
       </c>
       <c r="H8" t="n">
-        <v>128.7</v>
+        <v>131.2</v>
       </c>
     </row>
     <row r="9">
@@ -3185,19 +3229,19 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>26.2183</v>
+        <v>26.2595</v>
       </c>
       <c r="E9" t="n">
-        <v>5.4672</v>
+        <v>5.5451</v>
       </c>
       <c r="F9" t="n">
-        <v>27.868</v>
+        <v>27.9116</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3495</v>
+        <v>0.3494</v>
       </c>
       <c r="H9" t="n">
-        <v>128</v>
+        <v>128.7</v>
       </c>
     </row>
     <row r="10">
@@ -3212,22 +3256,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>20.0609</v>
+        <v>20.1879</v>
       </c>
       <c r="E10" t="n">
-        <v>4.227</v>
+        <v>3.2086</v>
       </c>
       <c r="F10" t="n">
-        <v>20.8223</v>
+        <v>20.9132</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3156</v>
+        <v>0.2847</v>
       </c>
       <c r="H10" t="n">
-        <v>123</v>
+        <v>136.8</v>
       </c>
     </row>
   </sheetData>
